--- a/education_forms/034_documentation_team_social_media_reporter_application--education_forms.xlsx
+++ b/education_forms/034_documentation_team_social_media_reporter_application--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'johndoe'}</t>
+          <t>johndoe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'johndoe'}</t>
+          <t>johndoe</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'janesmith'}</t>
+          <t>janesmith</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'janesmith'}</t>
+          <t>janesmith</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'website'}</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'website'}</t>
+          <t>website</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'blog'}</t>
+          <t>blog</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'blog'}</t>
+          <t>blog</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'newsletter'}</t>
+          <t>newsletter</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'newsletter'}</t>
+          <t>newsletter</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'url'}</t>
+          <t>url</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'url'}</t>
+          <t>url</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'link'}</t>
+          <t>link</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'link'}</t>
+          <t>link</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'reference'}</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'reference'}</t>
+          <t>reference</t>
         </is>
       </c>
     </row>
